--- a/output_data/charts/0500000US39073.xlsx
+++ b/output_data/charts/0500000US39073.xlsx
@@ -167,10 +167,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$15</c:f>
+              <c:f>Sheet1!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>2010</c:v>
                 </c:pt>
@@ -212,16 +212,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$2:$B$15</c:f>
+              <c:f>Sheet1!$B$2:$B$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>0.1729810399213106</c:v>
                 </c:pt>
@@ -253,16 +256,19 @@
                   <c:v>0.4001416430594901</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.4636233951497861</c:v>
+                  <c:v>0.4670897810739499</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.4697341731610975</c:v>
+                  <c:v>0.4731580632537621</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.4493493421525631</c:v>
+                  <c:v>0.4561290090866645</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.4611474219317357</c:v>
+                  <c:v>0.4715783364167302</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.4812424805862408</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -292,10 +298,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$15</c:f>
+              <c:f>Sheet1!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>2010</c:v>
                 </c:pt>
@@ -337,16 +343,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$C$2:$C$15</c:f>
+              <c:f>Sheet1!$C$2:$C$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>0.7868941423871383</c:v>
                 </c:pt>
@@ -378,16 +387,19 @@
                   <c:v>0.6621813031161473</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.666904422253923</c:v>
+                  <c:v>0.6703273194038365</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.7401871819508202</c:v>
+                  <c:v>0.7470916788217297</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.7441225106046445</c:v>
+                  <c:v>0.7614122041446683</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.7734204793028322</c:v>
+                  <c:v>0.7980556462436972</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.8968609865470852</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -417,10 +429,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$15</c:f>
+              <c:f>Sheet1!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>2010</c:v>
                 </c:pt>
@@ -462,16 +474,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$D$2:$D$15</c:f>
+              <c:f>Sheet1!$D$2:$D$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>0.6783570192992572</c:v>
                 </c:pt>
@@ -503,16 +518,19 @@
                   <c:v>1.097733711048159</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.8666191155492154</c:v>
+                  <c:v>0.8628681451900448</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.9572613074267819</c:v>
+                  <c:v>0.9534312853534455</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.9849737579984184</c:v>
+                  <c:v>0.9733146571849298</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.9985475671750182</c:v>
+                  <c:v>0.9830594551456452</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.068212475846732</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -542,10 +560,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$15</c:f>
+              <c:f>Sheet1!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>2010</c:v>
                 </c:pt>
@@ -587,16 +605,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$E$2:$E$15</c:f>
+              <c:f>Sheet1!$E$2:$E$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>0.3052606586846657</c:v>
                 </c:pt>
@@ -628,16 +649,19 @@
                   <c:v>0.3222379603399433</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.3423680456490727</c:v>
+                  <c:v>0.3422948013977038</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.3380662609871535</c:v>
+                  <c:v>0.3379700451812587</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.377453447408153</c:v>
+                  <c:v>0.3771145350716518</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.3885257806826434</c:v>
+                  <c:v>0.3990278231218486</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.4083269532246892</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -667,10 +691,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$15</c:f>
+              <c:f>Sheet1!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>2010</c:v>
                 </c:pt>
@@ -712,16 +736,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$F$2:$F$15</c:f>
+              <c:f>Sheet1!$F$2:$F$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>1.007360173659397</c:v>
                 </c:pt>
@@ -753,16 +780,19 @@
                   <c:v>1.327903682719547</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.398002853067047</c:v>
+                  <c:v>1.397703772373957</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.434112665029714</c:v>
+                  <c:v>1.433704507453129</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.437917894888202</c:v>
+                  <c:v>1.454584635276371</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.470588235294118</c:v>
+                  <c:v>1.505423150868793</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.531226074592585</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -792,10 +822,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$15</c:f>
+              <c:f>Sheet1!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>2010</c:v>
                 </c:pt>
@@ -837,16 +867,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$G$2:$G$15</c:f>
+              <c:f>Sheet1!$G$2:$G$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>97.04914696604823</c:v>
                 </c:pt>
@@ -878,16 +911,19 @@
                   <c:v>96.18980169971671</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>96.26248216833095</c:v>
+                  <c:v>96.2597161805605</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>96.06063841144443</c:v>
+                  <c:v>96.05464441993668</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>96.00618304694802</c:v>
+                  <c:v>95.97744495923571</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>95.90777051561365</c:v>
+                  <c:v>95.84285558820329</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>95.61413102920267</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1006,13 +1042,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1428750</xdr:colOff>
-      <xdr:row>37</xdr:row>
+      <xdr:row>38</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -1320,7 +1356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="40.7109375" style="1" customWidth="1"/>
@@ -1590,22 +1626,22 @@
         <v>2020</v>
       </c>
       <c r="B12" s="2">
-        <v>0.4636233951497861</v>
+        <v>0.4670897810739499</v>
       </c>
       <c r="C12" s="2">
-        <v>0.666904422253923</v>
+        <v>0.6703273194038365</v>
       </c>
       <c r="D12" s="2">
-        <v>0.8666191155492154</v>
+        <v>0.8628681451900448</v>
       </c>
       <c r="E12" s="2">
-        <v>0.3423680456490727</v>
+        <v>0.3422948013977038</v>
       </c>
       <c r="F12" s="2">
-        <v>1.398002853067047</v>
+        <v>1.397703772373957</v>
       </c>
       <c r="G12" s="2">
-        <v>96.26248216833095</v>
+        <v>96.2597161805605</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -1613,22 +1649,22 @@
         <v>2021</v>
       </c>
       <c r="B13" s="2">
-        <v>0.4697341731610975</v>
+        <v>0.4731580632537621</v>
       </c>
       <c r="C13" s="2">
-        <v>0.7401871819508202</v>
+        <v>0.7470916788217297</v>
       </c>
       <c r="D13" s="2">
-        <v>0.9572613074267819</v>
+        <v>0.9534312853534455</v>
       </c>
       <c r="E13" s="2">
-        <v>0.3380662609871535</v>
+        <v>0.3379700451812587</v>
       </c>
       <c r="F13" s="2">
-        <v>1.434112665029714</v>
+        <v>1.433704507453129</v>
       </c>
       <c r="G13" s="2">
-        <v>96.06063841144443</v>
+        <v>96.05464441993668</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -1636,22 +1672,22 @@
         <v>2022</v>
       </c>
       <c r="B14" s="2">
-        <v>0.4493493421525631</v>
+        <v>0.4561290090866645</v>
       </c>
       <c r="C14" s="2">
-        <v>0.7441225106046445</v>
+        <v>0.7614122041446683</v>
       </c>
       <c r="D14" s="2">
-        <v>0.9849737579984184</v>
+        <v>0.9733146571849298</v>
       </c>
       <c r="E14" s="2">
-        <v>0.377453447408153</v>
+        <v>0.3771145350716518</v>
       </c>
       <c r="F14" s="2">
-        <v>1.437917894888202</v>
+        <v>1.454584635276371</v>
       </c>
       <c r="G14" s="2">
-        <v>96.00618304694802</v>
+        <v>95.97744495923571</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -1659,22 +1695,45 @@
         <v>2023</v>
       </c>
       <c r="B15" s="2">
-        <v>0.4611474219317357</v>
+        <v>0.4715783364167302</v>
       </c>
       <c r="C15" s="2">
-        <v>0.7734204793028322</v>
+        <v>0.7980556462436972</v>
       </c>
       <c r="D15" s="2">
-        <v>0.9985475671750182</v>
+        <v>0.9830594551456452</v>
       </c>
       <c r="E15" s="2">
-        <v>0.3885257806826434</v>
+        <v>0.3990278231218486</v>
       </c>
       <c r="F15" s="2">
-        <v>1.470588235294118</v>
+        <v>1.505423150868793</v>
       </c>
       <c r="G15" s="2">
-        <v>95.90777051561365</v>
+        <v>95.84285558820329</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="3">
+        <v>2024</v>
+      </c>
+      <c r="B16" s="2">
+        <v>0.4812424805862408</v>
+      </c>
+      <c r="C16" s="2">
+        <v>0.8968609865470852</v>
+      </c>
+      <c r="D16" s="2">
+        <v>1.068212475846732</v>
+      </c>
+      <c r="E16" s="2">
+        <v>0.4083269532246892</v>
+      </c>
+      <c r="F16" s="2">
+        <v>1.531226074592585</v>
+      </c>
+      <c r="G16" s="2">
+        <v>95.61413102920267</v>
       </c>
     </row>
   </sheetData>

--- a/output_data/charts/0500000US39073.xlsx
+++ b/output_data/charts/0500000US39073.xlsx
@@ -226,34 +226,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>0.1729810399213106</c:v>
+                  <c:v>0.1764027410272067</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.1866241389840861</c:v>
+                  <c:v>0.190049548632322</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.2047082906857728</c:v>
+                  <c:v>0.2047502047502048</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.2163293789253315</c:v>
+                  <c:v>0.216382228736956</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.2295732025461755</c:v>
+                  <c:v>0.2296211251435132</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.2526138516595327</c:v>
+                  <c:v>0.256140350877193</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.3203886913354223</c:v>
+                  <c:v>0.3134575423519881</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.3586497890295359</c:v>
+                  <c:v>0.3516669011112674</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.3703311818855148</c:v>
+                  <c:v>0.370278943470748</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.4001416430594901</c:v>
+                  <c:v>0.3891876592131333</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>0.4670897810739499</c:v>
@@ -357,34 +357,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>0.7868941423871383</c:v>
+                  <c:v>0.7836352534093223</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.7940008822232024</c:v>
+                  <c:v>0.7975293558677798</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.8256567724326168</c:v>
+                  <c:v>0.8326508326508327</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.5652477320307048</c:v>
+                  <c:v>0.5793459672634629</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.5878465337924798</c:v>
+                  <c:v>0.5984065685558223</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.6034664234088836</c:v>
+                  <c:v>0.6245614035087719</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.6266943632714854</c:v>
+                  <c:v>0.6515690487091889</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.6188466947960619</c:v>
+                  <c:v>0.6541004360669573</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.6348534546608825</c:v>
+                  <c:v>0.6700285643756392</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.6621813031161473</c:v>
+                  <c:v>0.6934616473252194</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>0.6703273194038365</c:v>
@@ -488,34 +488,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>0.6783570192992572</c:v>
+                  <c:v>0.678472080873872</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.7532828882630382</c:v>
+                  <c:v>0.7534107106495622</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.7813033094506995</c:v>
+                  <c:v>0.7848757848757848</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.8583391486392185</c:v>
+                  <c:v>0.8655289149478239</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.8626387004765383</c:v>
+                  <c:v>0.8732560971366942</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.8841484808083644</c:v>
+                  <c:v>0.9017543859649122</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.8977924867091505</c:v>
+                  <c:v>0.9192406579086395</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.9423347398030942</c:v>
+                  <c:v>0.9741173160782107</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.022819454731422</c:v>
+                  <c:v>1.072045703001023</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.097733711048159</c:v>
+                  <c:v>1.139258420605717</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>0.8628681451900448</c:v>
@@ -619,34 +619,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>0.3052606586846657</c:v>
+                  <c:v>0.3053124363932424</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.3053849547012317</c:v>
+                  <c:v>0.3054367745876604</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.3036506311838963</c:v>
+                  <c:v>0.3037128037128037</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.3105373342637823</c:v>
+                  <c:v>0.3141032352633232</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.3130543671084212</c:v>
+                  <c:v>0.3235570399749504</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.3017332117044418</c:v>
+                  <c:v>0.3122807017543859</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.3063056719360631</c:v>
+                  <c:v>0.3134575423519881</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.3270042194092827</c:v>
+                  <c:v>0.3376002250668167</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.3491694000634853</c:v>
+                  <c:v>0.3596995450858694</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.3222379603399433</c:v>
+                  <c:v>0.3396546844041891</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>0.3422948013977038</c:v>
@@ -750,34 +750,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>1.007360173659397</c:v>
+                  <c:v>1.010923400502069</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.021343015167453</c:v>
+                  <c:v>1.028303807778457</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.05424769703173</c:v>
+                  <c:v>1.064701064701065</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.137473831123517</c:v>
+                  <c:v>1.151711862632185</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.200041740582281</c:v>
+                  <c:v>1.224646000765404</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.238509578275209</c:v>
+                  <c:v>1.270175438596491</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.26747174594233</c:v>
+                  <c:v>1.29961610256049</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.283403656821378</c:v>
+                  <c:v>1.332817555211704</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.28028780023278</c:v>
+                  <c:v>1.333004196494693</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.327903682719547</c:v>
+                  <c:v>1.386923294650439</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>1.397703772373957</c:v>
@@ -881,34 +881,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>97.04914696604823</c:v>
+                  <c:v>97.04525408779429</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>96.93936412066098</c:v>
+                  <c:v>96.92526980248421</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>96.83043329921529</c:v>
+                  <c:v>96.80930930930931</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>96.91207257501745</c:v>
+                  <c:v>96.87292779115624</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>96.80684545549411</c:v>
+                  <c:v>96.75051316842361</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>96.71952845414357</c:v>
+                  <c:v>96.63508771929824</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>96.58134704080555</c:v>
+                  <c:v>96.5026591061177</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>96.46976090014064</c:v>
+                  <c:v>96.34969756646504</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>96.34253870842592</c:v>
+                  <c:v>96.19494304757202</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>96.18980169971671</c:v>
+                  <c:v>96.0515142938013</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>96.2597161805605</c:v>
@@ -1396,22 +1396,22 @@
         <v>2010</v>
       </c>
       <c r="B2" s="2">
-        <v>0.1729810399213106</v>
+        <v>0.1764027410272067</v>
       </c>
       <c r="C2" s="2">
-        <v>0.7868941423871383</v>
+        <v>0.7836352534093223</v>
       </c>
       <c r="D2" s="2">
-        <v>0.6783570192992572</v>
+        <v>0.678472080873872</v>
       </c>
       <c r="E2" s="2">
-        <v>0.3052606586846657</v>
+        <v>0.3053124363932424</v>
       </c>
       <c r="F2" s="2">
-        <v>1.007360173659397</v>
+        <v>1.010923400502069</v>
       </c>
       <c r="G2" s="2">
-        <v>97.04914696604823</v>
+        <v>97.04525408779429</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -1419,22 +1419,22 @@
         <v>2011</v>
       </c>
       <c r="B3" s="2">
-        <v>0.1866241389840861</v>
+        <v>0.190049548632322</v>
       </c>
       <c r="C3" s="2">
-        <v>0.7940008822232024</v>
+        <v>0.7975293558677798</v>
       </c>
       <c r="D3" s="2">
-        <v>0.7532828882630382</v>
+        <v>0.7534107106495622</v>
       </c>
       <c r="E3" s="2">
-        <v>0.3053849547012317</v>
+        <v>0.3054367745876604</v>
       </c>
       <c r="F3" s="2">
-        <v>1.021343015167453</v>
+        <v>1.028303807778457</v>
       </c>
       <c r="G3" s="2">
-        <v>96.93936412066098</v>
+        <v>96.92526980248421</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1442,22 +1442,22 @@
         <v>2012</v>
       </c>
       <c r="B4" s="2">
-        <v>0.2047082906857728</v>
+        <v>0.2047502047502048</v>
       </c>
       <c r="C4" s="2">
-        <v>0.8256567724326168</v>
+        <v>0.8326508326508327</v>
       </c>
       <c r="D4" s="2">
-        <v>0.7813033094506995</v>
+        <v>0.7848757848757848</v>
       </c>
       <c r="E4" s="2">
-        <v>0.3036506311838963</v>
+        <v>0.3037128037128037</v>
       </c>
       <c r="F4" s="2">
-        <v>1.05424769703173</v>
+        <v>1.064701064701065</v>
       </c>
       <c r="G4" s="2">
-        <v>96.83043329921529</v>
+        <v>96.80930930930931</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -1465,22 +1465,22 @@
         <v>2013</v>
       </c>
       <c r="B5" s="2">
-        <v>0.2163293789253315</v>
+        <v>0.216382228736956</v>
       </c>
       <c r="C5" s="2">
-        <v>0.5652477320307048</v>
+        <v>0.5793459672634629</v>
       </c>
       <c r="D5" s="2">
-        <v>0.8583391486392185</v>
+        <v>0.8655289149478239</v>
       </c>
       <c r="E5" s="2">
-        <v>0.3105373342637823</v>
+        <v>0.3141032352633232</v>
       </c>
       <c r="F5" s="2">
-        <v>1.137473831123517</v>
+        <v>1.151711862632185</v>
       </c>
       <c r="G5" s="2">
-        <v>96.91207257501745</v>
+        <v>96.87292779115624</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -1488,22 +1488,22 @@
         <v>2014</v>
       </c>
       <c r="B6" s="2">
-        <v>0.2295732025461755</v>
+        <v>0.2296211251435132</v>
       </c>
       <c r="C6" s="2">
-        <v>0.5878465337924798</v>
+        <v>0.5984065685558223</v>
       </c>
       <c r="D6" s="2">
-        <v>0.8626387004765383</v>
+        <v>0.8732560971366942</v>
       </c>
       <c r="E6" s="2">
-        <v>0.3130543671084212</v>
+        <v>0.3235570399749504</v>
       </c>
       <c r="F6" s="2">
-        <v>1.200041740582281</v>
+        <v>1.224646000765404</v>
       </c>
       <c r="G6" s="2">
-        <v>96.80684545549411</v>
+        <v>96.75051316842361</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1511,22 +1511,22 @@
         <v>2015</v>
       </c>
       <c r="B7" s="2">
-        <v>0.2526138516595327</v>
+        <v>0.256140350877193</v>
       </c>
       <c r="C7" s="2">
-        <v>0.6034664234088836</v>
+        <v>0.6245614035087719</v>
       </c>
       <c r="D7" s="2">
-        <v>0.8841484808083644</v>
+        <v>0.9017543859649122</v>
       </c>
       <c r="E7" s="2">
-        <v>0.3017332117044418</v>
+        <v>0.3122807017543859</v>
       </c>
       <c r="F7" s="2">
-        <v>1.238509578275209</v>
+        <v>1.270175438596491</v>
       </c>
       <c r="G7" s="2">
-        <v>96.71952845414357</v>
+        <v>96.63508771929824</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1534,22 +1534,22 @@
         <v>2016</v>
       </c>
       <c r="B8" s="2">
-        <v>0.3203886913354223</v>
+        <v>0.3134575423519881</v>
       </c>
       <c r="C8" s="2">
-        <v>0.6266943632714854</v>
+        <v>0.6515690487091889</v>
       </c>
       <c r="D8" s="2">
-        <v>0.8977924867091505</v>
+        <v>0.9192406579086395</v>
       </c>
       <c r="E8" s="2">
-        <v>0.3063056719360631</v>
+        <v>0.3134575423519881</v>
       </c>
       <c r="F8" s="2">
-        <v>1.26747174594233</v>
+        <v>1.29961610256049</v>
       </c>
       <c r="G8" s="2">
-        <v>96.58134704080555</v>
+        <v>96.5026591061177</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -1557,22 +1557,22 @@
         <v>2017</v>
       </c>
       <c r="B9" s="2">
-        <v>0.3586497890295359</v>
+        <v>0.3516669011112674</v>
       </c>
       <c r="C9" s="2">
-        <v>0.6188466947960619</v>
+        <v>0.6541004360669573</v>
       </c>
       <c r="D9" s="2">
-        <v>0.9423347398030942</v>
+        <v>0.9741173160782107</v>
       </c>
       <c r="E9" s="2">
-        <v>0.3270042194092827</v>
+        <v>0.3376002250668167</v>
       </c>
       <c r="F9" s="2">
-        <v>1.283403656821378</v>
+        <v>1.332817555211704</v>
       </c>
       <c r="G9" s="2">
-        <v>96.46976090014064</v>
+        <v>96.34969756646504</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -1580,22 +1580,22 @@
         <v>2018</v>
       </c>
       <c r="B10" s="2">
-        <v>0.3703311818855148</v>
+        <v>0.370278943470748</v>
       </c>
       <c r="C10" s="2">
-        <v>0.6348534546608825</v>
+        <v>0.6700285643756392</v>
       </c>
       <c r="D10" s="2">
-        <v>1.022819454731422</v>
+        <v>1.072045703001023</v>
       </c>
       <c r="E10" s="2">
-        <v>0.3491694000634853</v>
+        <v>0.3596995450858694</v>
       </c>
       <c r="F10" s="2">
-        <v>1.28028780023278</v>
+        <v>1.333004196494693</v>
       </c>
       <c r="G10" s="2">
-        <v>96.34253870842592</v>
+        <v>96.19494304757202</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -1603,22 +1603,22 @@
         <v>2019</v>
       </c>
       <c r="B11" s="2">
-        <v>0.4001416430594901</v>
+        <v>0.3891876592131333</v>
       </c>
       <c r="C11" s="2">
-        <v>0.6621813031161473</v>
+        <v>0.6934616473252194</v>
       </c>
       <c r="D11" s="2">
-        <v>1.097733711048159</v>
+        <v>1.139258420605717</v>
       </c>
       <c r="E11" s="2">
-        <v>0.3222379603399433</v>
+        <v>0.3396546844041891</v>
       </c>
       <c r="F11" s="2">
-        <v>1.327903682719547</v>
+        <v>1.386923294650439</v>
       </c>
       <c r="G11" s="2">
-        <v>96.18980169971671</v>
+        <v>96.0515142938013</v>
       </c>
     </row>
     <row r="12" spans="1:7">
